--- a/Bibsam_tidskriftslistor/scifree_data_springernature.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_springernature.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\larher\Documents\GitHub\oa-tskr\Bibsam_tidskriftslistor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30DD1F39-50F9-481F-BCF3-45F11BC78C16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F7E0188-FBCF-4EDC-B029-DEE0A8231FEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A31CA459-7051-4FD4-B348-B8BA2BDE0027}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18335" uniqueCount="10034">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18336" uniqueCount="10034">
   <si>
     <t>Imprint</t>
   </si>
@@ -30173,8 +30173,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -84219,6 +84220,9 @@
       <c r="D2444" t="s">
         <v>10009</v>
       </c>
+      <c r="E2444" s="1" t="s">
+        <v>10012</v>
+      </c>
       <c r="F2444" t="s">
         <v>18</v>
       </c>
